--- a/tests/perf_v2/perf_history/v2.4.2/multi_label_cls/MULTI_LABEL_CLS-raw-multilabel_large_aid.xlsx
+++ b/tests/perf_v2/perf_history/v2.4.2/multi_label_cls/MULTI_LABEL_CLS-raw-multilabel_large_aid.xlsx
@@ -583,53 +583,53 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C2" t="n">
-        <v>134.3348956108093</v>
+        <v>146.1976053714752</v>
       </c>
       <c r="D2" t="n">
-        <v>1.870000004768372</v>
+        <v>1.809999942779541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.924117624759674</v>
+        <v>0.9278431534767152</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9262745380401612</v>
+        <v>0.9323529601097108</v>
       </c>
       <c r="G2" t="n">
-        <v>0.927450954914093</v>
+        <v>0.9343137145042421</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9258823394775392</v>
+        <v>0.931176483631134</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1009901505229728</v>
+        <v>0.0827974716352449</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1547861993312835</v>
+        <v>0.1496782749891281</v>
       </c>
       <c r="K2" t="n">
-        <v>25.04875755310058</v>
+        <v>21.92828369140625</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009143584569295199</v>
+        <v>0.008364547093709301</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0141376320521036</v>
+        <v>0.0141554498672485</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0193702673912048</v>
+        <v>0.019287249247233</v>
       </c>
       <c r="O2" t="n">
-        <v>4.241289615631104</v>
+        <v>4.246634960174561</v>
       </c>
       <c r="P2" t="n">
-        <v>5.81108021736145</v>
+        <v>5.786174774169922</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-132301</t>
+          <t>20250714-174708</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -674,13 +674,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -690,7 +692,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -699,53 +701,53 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
-        <v>161.983167886734</v>
+        <v>88.92787647247314</v>
       </c>
       <c r="D3" t="n">
-        <v>1.720000028610229</v>
+        <v>1.809999942779541</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9282352924346924</v>
+        <v>0.9256862998008728</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9280391931533812</v>
+        <v>0.9270588159561156</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9276470541954041</v>
+        <v>0.9284313917160034</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9284313917160034</v>
+        <v>0.9254902005195618</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1007456177955164</v>
+        <v>0.0818298626691102</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1505123227834701</v>
+        <v>0.1484318226575851</v>
       </c>
       <c r="K3" t="n">
-        <v>24.24798679351806</v>
+        <v>23.10312032699585</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008971136411031</v>
+        <v>0.0081797417004903</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0144754942258199</v>
+        <v>0.0152666703859965</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0193139298756917</v>
+        <v>0.0181656471888224</v>
       </c>
       <c r="O3" t="n">
-        <v>4.342648267745972</v>
+        <v>4.58000111579895</v>
       </c>
       <c r="P3" t="n">
-        <v>5.79417896270752</v>
+        <v>5.449694156646729</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-132634</t>
+          <t>20250714-175034</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -790,13 +792,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -806,7 +810,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -815,53 +819,53 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>147.1557302474976</v>
+        <v>100.403653383255</v>
       </c>
       <c r="D4" t="n">
-        <v>1.789999961853027</v>
+        <v>1.809999942779541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9319607615470886</v>
+        <v>0.9250980615615844</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9276470541954041</v>
+        <v>0.924117624759674</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9266666769981384</v>
+        <v>0.9247058629989624</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9258823394775392</v>
+        <v>0.9231372475624084</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1008471733620089</v>
+        <v>0.0819064742326736</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1674234718084335</v>
+        <v>0.1415458619594574</v>
       </c>
       <c r="K4" t="n">
-        <v>26.19853115081787</v>
+        <v>22.49406504631042</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0091643945376078</v>
+        <v>0.008151429494222</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0166594672203063</v>
+        <v>0.0142471011479695</v>
       </c>
       <c r="N4" t="n">
-        <v>0.020540444056193</v>
+        <v>0.0197742215792338</v>
       </c>
       <c r="O4" t="n">
-        <v>4.997840166091919</v>
+        <v>4.274130344390869</v>
       </c>
       <c r="P4" t="n">
-        <v>6.16213321685791</v>
+        <v>5.932266473770142</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-133033</t>
+          <t>20250714-175303</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -906,13 +910,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -922,7 +928,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -931,53 +937,53 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>162.2492744922638</v>
+        <v>192.4140782356262</v>
       </c>
       <c r="D5" t="n">
-        <v>1.740000009536743</v>
+        <v>1.960000038146973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.927450954914093</v>
+        <v>0.9313725233078004</v>
       </c>
       <c r="F5" t="n">
         <v>0.9303921461105348</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9288235306739808</v>
+        <v>0.9321568608283995</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9262745380401612</v>
+        <v>0.9278431534767152</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1016044530141002</v>
+        <v>0.0820787385562244</v>
       </c>
       <c r="J5" t="n">
-        <v>0.153110459446907</v>
+        <v>0.1537349671125412</v>
       </c>
       <c r="K5" t="n">
-        <v>25.0232949256897</v>
+        <v>22.7066662311554</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008918313185373899</v>
+        <v>0.0079686188697814</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0141371329625447</v>
+        <v>0.013707054456075</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0175535790125528</v>
+        <v>0.0188464546203613</v>
       </c>
       <c r="O5" t="n">
-        <v>4.241139888763428</v>
+        <v>4.11211633682251</v>
       </c>
       <c r="P5" t="n">
-        <v>5.266073703765869</v>
+        <v>5.653936386108398</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-133421</t>
+          <t>20250714-175543</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1022,13 +1028,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1038,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1047,53 +1055,53 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>106.8910310268402</v>
+        <v>129.0280487537384</v>
       </c>
       <c r="D6" t="n">
-        <v>1.629999995231628</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="E6" t="n">
         <v>0.9276470541954041</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9207842946052552</v>
+        <v>0.92607843875885</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9219607710838318</v>
+        <v>0.9268627166748048</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9194117784500122</v>
+        <v>0.9239215850830078</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1012399799444458</v>
+        <v>0.08300081560244919</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1702990382909774</v>
+        <v>0.1378505378961563</v>
       </c>
       <c r="K6" t="n">
-        <v>25.96711111068726</v>
+        <v>22.30472016334534</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0109220711390177</v>
+        <v>0.009044119517008399</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0158573770523071</v>
+        <v>0.014992438952128</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0183358573913574</v>
+        <v>0.018630785147349</v>
       </c>
       <c r="O6" t="n">
-        <v>4.757213115692139</v>
+        <v>4.497731685638428</v>
       </c>
       <c r="P6" t="n">
-        <v>5.500757217407227</v>
+        <v>5.589235544204712</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-133821</t>
+          <t>20250714-175955</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1138,13 +1146,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1154,7 +1164,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1324,53 +1334,53 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C2" t="n">
-        <v>135.1249775886536</v>
+        <v>123.4255855083466</v>
       </c>
       <c r="D2" t="n">
         <v>4.340000152587891</v>
       </c>
       <c r="E2" t="n">
-        <v>0.908431351184845</v>
+        <v>0.9039215445518494</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9070588350296021</v>
+        <v>0.8984313607215881</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9094117879867554</v>
+        <v>0.8992156982421875</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9064705967903136</v>
+        <v>0.9025490283966064</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1031112750726086</v>
+        <v>0.0902501294168374</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1711023896932602</v>
+        <v>0.1429266929626464</v>
       </c>
       <c r="K2" t="n">
-        <v>18.76137280464172</v>
+        <v>17.34326815605164</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0079497631390889</v>
+        <v>0.0070533887545267</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0127831308046976</v>
+        <v>0.0150759323438008</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0167704351743062</v>
+        <v>0.016531745592753</v>
       </c>
       <c r="O2" t="n">
-        <v>3.834939241409302</v>
+        <v>4.522779703140259</v>
       </c>
       <c r="P2" t="n">
-        <v>5.03113055229187</v>
+        <v>4.959523677825928</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-104016</t>
+          <t>20250714-152200</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -1415,13 +1425,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1431,7 +1443,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1440,53 +1452,53 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C3" t="n">
-        <v>209.9851262569427</v>
+        <v>206.6380507946014</v>
       </c>
       <c r="D3" t="n">
         <v>4.349999904632568</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9135293960571288</v>
+        <v>0.9090195894241332</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9150980114936828</v>
+        <v>0.9080392122268676</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9160784482955932</v>
+        <v>0.9115686416625975</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9133333563804626</v>
+        <v>0.9060784578323364</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1025689382399065</v>
+        <v>0.0891773412280743</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1562888771295547</v>
+        <v>0.1451053768396377</v>
       </c>
       <c r="K3" t="n">
-        <v>19.76111483573914</v>
+        <v>17.59692096710205</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008910202185312899</v>
+        <v>0.0069502401351928</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0134350109100341</v>
+        <v>0.013584447701772</v>
       </c>
       <c r="N3" t="n">
-        <v>0.016967069307963</v>
+        <v>0.0181682554880777</v>
       </c>
       <c r="O3" t="n">
-        <v>4.030503273010254</v>
+        <v>4.075334310531616</v>
       </c>
       <c r="P3" t="n">
-        <v>5.090120792388916</v>
+        <v>5.45047664642334</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-104329</t>
+          <t>20250714-152455</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1531,13 +1543,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1547,7 +1561,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1556,53 +1570,53 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="C4" t="n">
-        <v>143.0276067256927</v>
+        <v>174.7024199962616</v>
       </c>
       <c r="D4" t="n">
-        <v>4.349999904632568</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9031372666358948</v>
+        <v>0.9107843041419984</v>
       </c>
       <c r="F4" t="n">
-        <v>0.905098021030426</v>
+        <v>0.91019606590271</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9060784578323364</v>
+        <v>0.9115686416625975</v>
       </c>
       <c r="H4" t="n">
-        <v>0.903529405593872</v>
+        <v>0.908627450466156</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1032626955943592</v>
+        <v>0.08835850179541931</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1745917946100235</v>
+        <v>0.1321953535079956</v>
       </c>
       <c r="K4" t="n">
-        <v>18.6442859172821</v>
+        <v>17.26914763450623</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008071273167928</v>
+        <v>0.0068203536669413</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0125000635782877</v>
+        <v>0.014024658203125</v>
       </c>
       <c r="N4" t="n">
-        <v>0.016510587533315</v>
+        <v>0.0178247221310933</v>
       </c>
       <c r="O4" t="n">
-        <v>3.750019073486328</v>
+        <v>4.2073974609375</v>
       </c>
       <c r="P4" t="n">
-        <v>4.953176259994507</v>
+        <v>5.347416639328003</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-104756</t>
+          <t>20250714-152914</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1647,13 +1661,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1663,7 +1679,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1672,53 +1688,53 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C5" t="n">
-        <v>143.1087222099304</v>
+        <v>145.4100260734558</v>
       </c>
       <c r="D5" t="n">
-        <v>4.349999904632568</v>
+        <v>4.389999866485596</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9049019813537598</v>
+        <v>0.9047058820724488</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9037255048751832</v>
+        <v>0.9076470732688904</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9052941203117372</v>
+        <v>0.9098039269447328</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.903529405593872</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1044701320134986</v>
+        <v>0.0882938878846839</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1619606912136078</v>
+        <v>0.1501536965370178</v>
       </c>
       <c r="K5" t="n">
-        <v>19.09735655784607</v>
+        <v>17.38426899909973</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0078319295247395</v>
+        <v>0.0070984864234924</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0131705602010091</v>
+        <v>0.0130269694328308</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0157765674591064</v>
+        <v>0.0181479732195536</v>
       </c>
       <c r="O5" t="n">
-        <v>3.951168060302734</v>
+        <v>3.908090829849243</v>
       </c>
       <c r="P5" t="n">
-        <v>4.732970237731934</v>
+        <v>5.444391965866089</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-105116</t>
+          <t>20250714-153301</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1763,13 +1779,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1779,7 +1797,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -1788,53 +1806,53 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C6" t="n">
-        <v>205.1874227523804</v>
+        <v>171.6868624687195</v>
       </c>
       <c r="D6" t="n">
-        <v>4.389999866485596</v>
+        <v>4.420000076293945</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9147058725357056</v>
+        <v>0.908431351184845</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9127451181411744</v>
+        <v>0.906862735748291</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9123529195785522</v>
+        <v>0.9092156887054444</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9135293960571288</v>
+        <v>0.9092156887054444</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1032137575364389</v>
+        <v>0.0894568655864301</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1622153371572494</v>
+        <v>0.1473215967416763</v>
       </c>
       <c r="K6" t="n">
-        <v>19.17501306533813</v>
+        <v>17.97013854980469</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008976346651712999</v>
+        <v>0.0069314940770467</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0130754081408182</v>
+        <v>0.0140307339032491</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0178131318092346</v>
+        <v>0.01687775293986</v>
       </c>
       <c r="O6" t="n">
-        <v>3.922622442245483</v>
+        <v>4.209220170974731</v>
       </c>
       <c r="P6" t="n">
-        <v>5.343939542770386</v>
+        <v>5.063325881958008</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-105436</t>
+          <t>20250714-153618</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1879,13 +1897,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1895,7 +1915,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2065,53 +2085,53 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C2" t="n">
-        <v>183.8065950870514</v>
+        <v>154.7466671466827</v>
       </c>
       <c r="D2" t="n">
-        <v>5.739999771118164</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9174509644508362</v>
+        <v>0.9150980114936828</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9164705872535706</v>
+        <v>0.9178431630134584</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9164705872535706</v>
+        <v>0.9196078181266784</v>
       </c>
       <c r="H2" t="n">
-        <v>0.916862726211548</v>
+        <v>0.9170588254928588</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1370282855074283</v>
+        <v>0.121661365165242</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1797739863395691</v>
+        <v>0.1411018669605255</v>
       </c>
       <c r="K2" t="n">
-        <v>46.72734498977661</v>
+        <v>41.05759859085083</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0122088901201883</v>
+        <v>0.01323788245519</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0186937459309895</v>
+        <v>0.0186116027832031</v>
       </c>
       <c r="N2" t="n">
-        <v>0.025722754796346</v>
+        <v>0.0239787117640177</v>
       </c>
       <c r="O2" t="n">
-        <v>5.608123779296875</v>
+        <v>5.583480834960938</v>
       </c>
       <c r="P2" t="n">
-        <v>7.716826438903809</v>
+        <v>7.193613529205322</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-114308</t>
+          <t>20250714-162217</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -2156,13 +2176,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -2172,7 +2194,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2181,53 +2203,53 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>130.3761882781982</v>
+        <v>163.1898357868195</v>
       </c>
       <c r="D3" t="n">
-        <v>5.710000038146973</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="E3" t="n">
-        <v>0.906862735748291</v>
+        <v>0.9113725423812866</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9094117879867554</v>
+        <v>0.91725492477417</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9137254953384401</v>
+        <v>0.9164705872535706</v>
       </c>
       <c r="H3" t="n">
-        <v>0.908431351184845</v>
+        <v>0.9160784482955932</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1393035806533766</v>
+        <v>0.12104903565625</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1703502386808395</v>
+        <v>0.1215037778019905</v>
       </c>
       <c r="K3" t="n">
-        <v>45.36765861511231</v>
+        <v>39.96114802360535</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0136511405309041</v>
+        <v>0.013447786172231</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0197381337483723</v>
+        <v>0.0177432584762573</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0259515357017517</v>
+        <v>0.0238350931803385</v>
       </c>
       <c r="O3" t="n">
-        <v>5.921440124511719</v>
+        <v>5.322977542877197</v>
       </c>
       <c r="P3" t="n">
-        <v>7.785460710525513</v>
+        <v>7.150527954101562</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-114754</t>
+          <t>20250714-162630</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -2272,13 +2294,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -2288,7 +2312,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2297,53 +2321,53 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
-        <v>176.5911569595337</v>
+        <v>147.0935251712799</v>
       </c>
       <c r="D4" t="n">
-        <v>5.739999771118164</v>
+        <v>5.75</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9137254953384401</v>
+        <v>0.911960780620575</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9111764430999756</v>
+        <v>0.9162744879722596</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9150980114936828</v>
+        <v>0.9170588254928588</v>
       </c>
       <c r="H4" t="n">
-        <v>0.912156879901886</v>
+        <v>0.9129411578178406</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1398106947807328</v>
+        <v>0.1223094883673595</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1790256202220916</v>
+        <v>0.145508125424385</v>
       </c>
       <c r="K4" t="n">
-        <v>46.91959762573242</v>
+        <v>40.0291748046875</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0122999167442321</v>
+        <v>0.0141186769803365</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0185909557342529</v>
+        <v>0.0183043392499287</v>
       </c>
       <c r="N4" t="n">
-        <v>0.025663837591807</v>
+        <v>0.023610135714213</v>
       </c>
       <c r="O4" t="n">
-        <v>5.577286720275879</v>
+        <v>5.491301774978638</v>
       </c>
       <c r="P4" t="n">
-        <v>7.699151277542114</v>
+        <v>7.083040714263916</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-115146</t>
+          <t>20250714-163051</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -2388,13 +2412,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2404,7 +2430,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2413,53 +2439,53 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C5" t="n">
-        <v>156.6991975307465</v>
+        <v>163.0043013095856</v>
       </c>
       <c r="D5" t="n">
-        <v>5.710000038146973</v>
+        <v>5.78000020980835</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9115686416625975</v>
+        <v>0.9166666865348816</v>
       </c>
       <c r="F5" t="n">
-        <v>0.91019606590271</v>
+        <v>0.9184314012527466</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9113725423812866</v>
+        <v>0.9227451086044312</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9090195894241332</v>
+        <v>0.9156862497329712</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1375132870674132</v>
+        <v>0.1219051691182588</v>
       </c>
       <c r="J5" t="n">
-        <v>0.170986458659172</v>
+        <v>0.1445761173963546</v>
       </c>
       <c r="K5" t="n">
-        <v>46.05205488204956</v>
+        <v>39.96662068367005</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0124612832069396</v>
+        <v>0.0139424339930216</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0183063475290934</v>
+        <v>0.0178553779919942</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0242826008796691</v>
+        <v>0.0247647945086161</v>
       </c>
       <c r="O5" t="n">
-        <v>5.491904258728027</v>
+        <v>5.356613397598267</v>
       </c>
       <c r="P5" t="n">
-        <v>7.284780263900757</v>
+        <v>7.429438352584839</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-115625</t>
+          <t>20250714-163454</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -2504,13 +2530,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2520,7 +2548,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2529,53 +2557,53 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>192.8481192588806</v>
+        <v>163.9419043064117</v>
       </c>
       <c r="D6" t="n">
-        <v>5.710000038146973</v>
+        <v>5.760000228881836</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9158823490142822</v>
+        <v>0.9186274409294128</v>
       </c>
       <c r="F6" t="n">
-        <v>0.915294110774994</v>
+        <v>0.9184314012527466</v>
       </c>
       <c r="G6" t="n">
-        <v>0.91725492477417</v>
+        <v>0.9209803938865662</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9156862497329712</v>
+        <v>0.9203921556472778</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1370876080566836</v>
+        <v>0.1227257361603995</v>
       </c>
       <c r="J6" t="n">
-        <v>0.176534354686737</v>
+        <v>0.1437439769506454</v>
       </c>
       <c r="K6" t="n">
-        <v>45.78541326522827</v>
+        <v>39.88992428779602</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0120056780179341</v>
+        <v>0.0140515462557474</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0186205673217773</v>
+        <v>0.0178279868761698</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0236295040448506</v>
+        <v>0.024382631778717</v>
       </c>
       <c r="O6" t="n">
-        <v>5.586170196533203</v>
+        <v>5.348396062850952</v>
       </c>
       <c r="P6" t="n">
-        <v>7.0888512134552</v>
+        <v>7.314789533615112</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-120043</t>
+          <t>20250714-163915</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -2620,13 +2648,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2636,7 +2666,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2809,50 +2839,50 @@
         <v>53</v>
       </c>
       <c r="C2" t="n">
-        <v>124.0486588478088</v>
+        <v>104.9520316123962</v>
       </c>
       <c r="D2" t="n">
         <v>2.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9133333563804626</v>
+        <v>0.9162744879722596</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9129411578178406</v>
+        <v>0.918823540210724</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9127451181411744</v>
+        <v>0.9200000166893004</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9066666960716248</v>
+        <v>0.9135293960571288</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0985106801930463</v>
+        <v>0.0816428534827142</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1688359677791595</v>
+        <v>0.1390467584133148</v>
       </c>
       <c r="K2" t="n">
-        <v>18.06600189208984</v>
+        <v>16.19658064842224</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008040805657704601</v>
+        <v>0.0064707978566487</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01369145154953</v>
+        <v>0.0128702624638875</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0175720731417338</v>
+        <v>0.0168411755561828</v>
       </c>
       <c r="O2" t="n">
-        <v>4.107435464859009</v>
+        <v>3.86107873916626</v>
       </c>
       <c r="P2" t="n">
-        <v>5.271621942520142</v>
+        <v>5.052352666854858</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20250714-123327</t>
+          <t>20250714-170550</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -2897,13 +2927,15 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -2913,7 +2945,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -2922,53 +2954,53 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
-        <v>166.163982629776</v>
+        <v>88.94263792037964</v>
       </c>
       <c r="D3" t="n">
-        <v>2.460000038146973</v>
+        <v>2.670000076293945</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9182353019714355</v>
+        <v>0.9143137335777284</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9219607710838318</v>
+        <v>0.9160784482955932</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9221568703651428</v>
+        <v>0.9145098328590392</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9200000166893004</v>
+        <v>0.9133333563804626</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1001973767095887</v>
+        <v>0.0820637302981181</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1742114573717117</v>
+        <v>0.1423436999320984</v>
       </c>
       <c r="K3" t="n">
-        <v>17.22551274299622</v>
+        <v>15.81122422218323</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0076463977495829</v>
+        <v>0.0064462280273437</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0138583238919576</v>
+        <v>0.0132422924041748</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0169835225741068</v>
+        <v>0.0154098447163899</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15749716758728</v>
+        <v>3.972687721252441</v>
       </c>
       <c r="P3" t="n">
-        <v>5.095056772232056</v>
+        <v>4.622953414916992</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>20250714-123626</t>
+          <t>20250714-170824</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -3013,13 +3045,15 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -3029,7 +3063,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -3038,53 +3072,53 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
-        <v>139.2914245128632</v>
+        <v>105.5022072792053</v>
       </c>
       <c r="D4" t="n">
-        <v>2.460000038146973</v>
+        <v>2.509999990463257</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9174509644508362</v>
+        <v>0.915294110774994</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9186274409294128</v>
+        <v>0.9137254953384401</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9180392026901244</v>
+        <v>0.9137254953384401</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9156862497329712</v>
+        <v>0.9127451181411744</v>
       </c>
       <c r="I4" t="n">
-        <v>0.100473926355273</v>
+        <v>0.0817936178085938</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0897038951516151</v>
+        <v>0.1490800529718399</v>
       </c>
       <c r="K4" t="n">
-        <v>18.04781746864319</v>
+        <v>15.95467591285706</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0087048077583312</v>
+        <v>0.0066624482472737</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0148428058624267</v>
+        <v>0.0130357193946838</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0163883924484252</v>
+        <v>0.0169313955307006</v>
       </c>
       <c r="O4" t="n">
-        <v>4.452841758728027</v>
+        <v>3.910715818405152</v>
       </c>
       <c r="P4" t="n">
-        <v>4.916517734527588</v>
+        <v>5.079418659210205</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20250714-124006</t>
+          <t>20250714-171042</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -3129,13 +3163,15 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -3145,7 +3181,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -3154,53 +3190,53 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C5" t="n">
-        <v>151.5084857940674</v>
+        <v>150.3287343978882</v>
       </c>
       <c r="D5" t="n">
-        <v>2.509999990463257</v>
+        <v>2.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9149019718170166</v>
+        <v>0.9213725328445436</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9160784482955932</v>
+        <v>0.9164705872535706</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9182353019714355</v>
+        <v>0.9178431630134584</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9137254953384401</v>
+        <v>0.91901957988739</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09936335086822499</v>
+        <v>0.0822705433933765</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1639161854982376</v>
+        <v>0.1476698964834213</v>
       </c>
       <c r="K5" t="n">
-        <v>18.49507188796997</v>
+        <v>15.65603947639465</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0077693359057108</v>
+        <v>0.0065379047393798</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0138517308235168</v>
+        <v>0.0141331799825032</v>
       </c>
       <c r="N5" t="n">
-        <v>0.016532867749532</v>
+        <v>0.0159713570276896</v>
       </c>
       <c r="O5" t="n">
-        <v>4.155519247055054</v>
+        <v>4.239953994750977</v>
       </c>
       <c r="P5" t="n">
-        <v>4.959860324859619</v>
+        <v>4.791407108306885</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20250714-124321</t>
+          <t>20250714-171316</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -3245,13 +3281,15 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -3261,7 +3299,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
@@ -3270,53 +3308,53 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C6" t="n">
-        <v>152.0206828117371</v>
+        <v>166.1470494270325</v>
       </c>
       <c r="D6" t="n">
-        <v>2.460000038146973</v>
+        <v>2.630000114440918</v>
       </c>
       <c r="E6" t="n">
-        <v>0.913921594619751</v>
+        <v>0.9201960563659668</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9182353019714355</v>
+        <v>0.9247058629989624</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9174509644508362</v>
+        <v>0.9247058629989624</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9178431630134584</v>
+        <v>0.9258823394775392</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09973050757096349</v>
+        <v>0.08137791023351421</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1755650341510772</v>
+        <v>0.1401407122611999</v>
       </c>
       <c r="K6" t="n">
-        <v>16.95107126235962</v>
+        <v>15.91201877593994</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0077104981740315</v>
+        <v>0.0066502714157104</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0141602071126302</v>
+        <v>0.0131571793556213</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0165315715471903</v>
+        <v>0.0156606944402058</v>
       </c>
       <c r="O6" t="n">
-        <v>4.248062133789063</v>
+        <v>3.947153806686402</v>
       </c>
       <c r="P6" t="n">
-        <v>4.959471464157104</v>
+        <v>4.698208332061768</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20250714-124648</t>
+          <t>20250714-171636</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -3361,13 +3399,15 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10920X CPU @ 3.50GHz</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-05cdff42-f2a4-cbdc-8348-ff432981e5d6)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-936e0f33-79be-50a3-4a95-4f28588fb9fe)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-ade58e12-4e2e-548c-e3db-b31d442cc38a)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-3f62614b-2618-9e2e-c8ed-fed7c7141571)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-5c1eec90-64a0-4585-f87a-4cc4d8352d1a)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-67e35a85-c92c-e2a6-5619-1ab85b318d99)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -3377,7 +3417,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>iotg-dev-workstation-11</t>
+          <t>workstation10</t>
         </is>
       </c>
     </row>
